--- a/data/trans_orig/P6703-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6703-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tiene tiempo de llevar al día su trabajo en 2012</t>
+          <t>Población según si tiene tiempo de llevar al día su trabajo en 2012 (tasa de respuesta: 99,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9469</t>
+          <t>9285</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11896</t>
+          <t>10810</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2819</t>
+          <t>2888</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16163</t>
+          <t>18081</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10672</t>
+          <t>10692</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10977</t>
+          <t>11334</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5019</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17875</t>
+          <t>16961</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38735</t>
+          <t>39428</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>64307</t>
+          <t>63573</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20196</t>
+          <t>21000</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>40742</t>
+          <t>41774</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>64224</t>
+          <t>64784</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>94938</t>
+          <t>96559</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66534</t>
+          <t>66621</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>98021</t>
+          <t>99188</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38365</t>
+          <t>38512</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>62106</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>111950</t>
+          <t>113503</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>152020</t>
+          <t>152548</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,46%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>111734</t>
+          <t>111100</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>144301</t>
+          <t>144753</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60901</t>
+          <t>59463</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>86785</t>
+          <t>85740</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>179720</t>
+          <t>181254</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>221734</t>
+          <t>221825</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,56%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11434</t>
+          <t>11414</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14072</t>
+          <t>13007</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5525</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19135</t>
+          <t>19938</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5091</t>
+          <t>5690</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18582</t>
+          <t>20081</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4486</t>
+          <t>4490</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17755</t>
+          <t>17740</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12730</t>
+          <t>12752</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30795</t>
+          <t>32512</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>57298</t>
+          <t>56602</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>87404</t>
+          <t>88900</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34544</t>
+          <t>33646</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59961</t>
+          <t>60843</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>99043</t>
+          <t>99748</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>138276</t>
+          <t>139771</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>97338</t>
+          <t>99083</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>134374</t>
+          <t>139032</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69109</t>
+          <t>69500</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101120</t>
+          <t>102065</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>175902</t>
+          <t>176664</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>225863</t>
+          <t>226103</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>185628</t>
+          <t>184302</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>226901</t>
+          <t>227135</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>107618</t>
+          <t>107762</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>142872</t>
+          <t>141336</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>304325</t>
+          <t>302289</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>360192</t>
+          <t>358092</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>52,56%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12619</t>
+          <t>13332</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2272</t>
+          <t>2359</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>15645</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7314</t>
+          <t>7248</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23654</t>
+          <t>23550</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16533</t>
+          <t>17103</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>2899</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>12979</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>6214</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23306</t>
+          <t>24182</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36063</t>
+          <t>36694</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62979</t>
+          <t>64373</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19100</t>
+          <t>19102</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>39673</t>
+          <t>39814</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>61094</t>
+          <t>59646</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>95407</t>
+          <t>94576</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,62%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>73427</t>
+          <t>74930</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>109473</t>
+          <t>109537</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50831</t>
+          <t>50232</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79628</t>
+          <t>80016</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>135625</t>
+          <t>135188</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>182206</t>
+          <t>178363</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,23%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>151262</t>
+          <t>148335</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>188114</t>
+          <t>188626</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>92442</t>
+          <t>92555</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>123206</t>
+          <t>122146</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>254929</t>
+          <t>252324</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>302636</t>
+          <t>299504</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>55,8%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6632</t>
+          <t>6982</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22240</t>
+          <t>22979</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6696</t>
+          <t>6768</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20882</t>
+          <t>21134</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17017</t>
+          <t>16614</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38137</t>
+          <t>38037</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>6830</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21029</t>
+          <t>21062</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6830</t>
+          <t>6851</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>21625</t>
+          <t>20308</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>16449</t>
+          <t>16367</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>37365</t>
+          <t>35809</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>83749</t>
+          <t>81684</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>121100</t>
+          <t>117964</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>56583</t>
+          <t>56371</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>86553</t>
+          <t>85058</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>148376</t>
+          <t>147810</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>192910</t>
+          <t>192868</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,7%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>117789</t>
+          <t>119027</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>157983</t>
+          <t>158555</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>66565</t>
+          <t>65647</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>98087</t>
+          <t>97632</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>194582</t>
+          <t>192055</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>244456</t>
+          <t>245811</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,03%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>137945</t>
+          <t>137516</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>177626</t>
+          <t>177884</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>107859</t>
+          <t>109430</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>142821</t>
+          <t>143604</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>254267</t>
+          <t>257693</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>310533</t>
+          <t>311842</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>43,17%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>18770</t>
+          <t>18657</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>40247</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>19288</t>
+          <t>20062</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>43304</t>
+          <t>43226</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>42878</t>
+          <t>42199</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>75948</t>
+          <t>75410</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24774</t>
+          <t>24167</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>50764</t>
+          <t>49097</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,82 +3588,82 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>33761</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>23543</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>47785</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>2,48%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>5,04%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>68445</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>52717</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>84535</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
           <t>3,57%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>33761</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>23787</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>46482</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>68445</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>54750</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>88616</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>241046</t>
+          <t>239966</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>298755</t>
+          <t>299027</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>151406</t>
+          <t>147794</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>199494</t>
+          <t>198636</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>404712</t>
+          <t>406423</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>483306</t>
+          <t>482096</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,34%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>395258</t>
+          <t>393242</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>467128</t>
+          <t>467545</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>250109</t>
+          <t>248692</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>308514</t>
+          <t>306944</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>666865</t>
+          <t>664296</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>758185</t>
+          <t>757598</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,96%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>622227</t>
+          <t>617714</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>702925</t>
+          <t>697278</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>398675</t>
+          <t>397847</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>464588</t>
+          <t>466188</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1037062</t>
+          <t>1043574</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1140437</t>
+          <t>1144173</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,27%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tiene tiempo de llevar al día su trabajo en 2016</t>
+          <t>Población según si tiene tiempo de llevar al día su trabajo en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3860</t>
+          <t>3387</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15876</t>
+          <t>16115</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5310</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16249</t>
+          <t>17793</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10824</t>
+          <t>11585</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27392</t>
+          <t>29047</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7901</t>
+          <t>7940</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23340</t>
+          <t>23154</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7056</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20572</t>
+          <t>20556</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17740</t>
+          <t>17798</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37521</t>
+          <t>36304</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44709</t>
+          <t>45257</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>73580</t>
+          <t>71795</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20709</t>
+          <t>20423</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39568</t>
+          <t>39704</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>71852</t>
+          <t>71505</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>104948</t>
+          <t>104177</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,37%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62212</t>
+          <t>65002</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92656</t>
+          <t>94502</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34027</t>
+          <t>33876</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56208</t>
+          <t>54760</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>103325</t>
+          <t>105616</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>140757</t>
+          <t>141274</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,4%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>69605</t>
+          <t>68856</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>100819</t>
+          <t>98700</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>59570</t>
+          <t>59400</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>84482</t>
+          <t>83875</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>136152</t>
+          <t>137666</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>177867</t>
+          <t>175308</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>42,69%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>6466</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20352</t>
+          <t>22336</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4619</t>
+          <t>3971</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17390</t>
+          <t>16717</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13769</t>
+          <t>13888</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31861</t>
+          <t>33121</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14992</t>
+          <t>15122</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33439</t>
+          <t>33943</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7806</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22964</t>
+          <t>23506</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26434</t>
+          <t>26839</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50671</t>
+          <t>51746</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>57898</t>
+          <t>58167</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>90075</t>
+          <t>90970</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38939</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64114</t>
+          <t>63240</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>103904</t>
+          <t>102534</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>145493</t>
+          <t>145519</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>120498</t>
+          <t>122167</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>161002</t>
+          <t>162068</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67311</t>
+          <t>67695</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>97165</t>
+          <t>96868</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>199916</t>
+          <t>200419</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>249638</t>
+          <t>250129</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,37%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>142721</t>
+          <t>142382</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>185556</t>
+          <t>184745</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>101099</t>
+          <t>101978</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>134489</t>
+          <t>134400</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>255309</t>
+          <t>256338</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>309746</t>
+          <t>310189</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>45,1%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4257</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17004</t>
+          <t>16896</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3808</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14935</t>
+          <t>14053</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10622</t>
+          <t>10408</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27208</t>
+          <t>27046</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10555</t>
+          <t>9528</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29164</t>
+          <t>28396</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10658</t>
+          <t>11156</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28192</t>
+          <t>27929</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24990</t>
+          <t>23803</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49773</t>
+          <t>47762</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>62027</t>
+          <t>61309</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>93079</t>
+          <t>92659</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32877</t>
+          <t>32970</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>57216</t>
+          <t>58321</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>100916</t>
+          <t>101001</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>143156</t>
+          <t>141143</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,25%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>94196</t>
+          <t>93909</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>130503</t>
+          <t>130222</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54760</t>
+          <t>55432</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>81707</t>
+          <t>83327</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>158505</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>203781</t>
+          <t>205739</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,43%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>128354</t>
+          <t>129406</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>169441</t>
+          <t>169285</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>116343</t>
+          <t>115619</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>148375</t>
+          <t>147537</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>256514</t>
+          <t>253578</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>308001</t>
+          <t>306416</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,3%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5930</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19843</t>
+          <t>20420</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18130</t>
+          <t>17684</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13133</t>
+          <t>13373</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30936</t>
+          <t>31627</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12864</t>
+          <t>13766</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>30762</t>
+          <t>31178</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8874</t>
+          <t>8731</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>25369</t>
+          <t>24249</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>25098</t>
+          <t>25728</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>49755</t>
+          <t>50290</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>48331</t>
+          <t>47575</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>77439</t>
+          <t>77360</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>37688</t>
+          <t>38441</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>64303</t>
+          <t>64846</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>91603</t>
+          <t>93453</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>131968</t>
+          <t>133201</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,33%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>116234</t>
+          <t>116151</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>152774</t>
+          <t>153463</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>100094</t>
+          <t>99262</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>133757</t>
+          <t>134870</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>224228</t>
+          <t>227150</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>277486</t>
+          <t>277842</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,24%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>152464</t>
+          <t>152950</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>195065</t>
+          <t>192490</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>115235</t>
+          <t>115712</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>152326</t>
+          <t>151011</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>277849</t>
+          <t>279855</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>332245</t>
+          <t>333832</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,94%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>28913</t>
+          <t>29794</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>54359</t>
+          <t>56535</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>26026</t>
+          <t>26687</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>50268</t>
+          <t>51660</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>60861</t>
+          <t>59932</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>97089</t>
+          <t>95916</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>58221</t>
+          <t>58898</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>93307</t>
+          <t>94908</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>46609</t>
+          <t>46071</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>75880</t>
+          <t>76891</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>114816</t>
+          <t>112570</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>157965</t>
+          <t>158886</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>239738</t>
+          <t>241635</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>298754</t>
+          <t>302758</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>150902</t>
+          <t>150133</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>199766</t>
+          <t>198083</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>405991</t>
+          <t>405708</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>484601</t>
+          <t>485182</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>430931</t>
+          <t>432259</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>503677</t>
+          <t>503993</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>282819</t>
+          <t>282652</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>345351</t>
+          <t>343557</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>729134</t>
+          <t>730550</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>821641</t>
+          <t>823800</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,49%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>530953</t>
+          <t>531787</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>606284</t>
+          <t>607872</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>424725</t>
+          <t>422213</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>487633</t>
+          <t>486106</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>974869</t>
+          <t>978164</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1073140</t>
+          <t>1082131</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>44,0%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tiene tiempo de llevar al día su trabajo en 2023</t>
+          <t>Población según si tiene tiempo de llevar al día su trabajo en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7861</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11586</t>
+          <t>10459</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2417</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12680</t>
+          <t>13362</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>2647</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13880</t>
+          <t>14044</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3921</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3601</t>
+          <t>3464</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14560</t>
+          <t>14192</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11586</t>
+          <t>12074</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6055</t>
+          <t>5827</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16248</t>
+          <t>15805</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9770</t>
+          <t>10198</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22400</t>
+          <t>23736</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>15,07%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14676</t>
+          <t>15570</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37505</t>
+          <t>37738</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11889</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25757</t>
+          <t>26197</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30270</t>
+          <t>29521</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58235</t>
+          <t>56968</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,18%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39901</t>
+          <t>38920</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>62424</t>
+          <t>62140</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26947</t>
+          <t>27183</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41655</t>
+          <t>41527</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>71298</t>
+          <t>71484</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>99212</t>
+          <t>99895</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>63,44%</t>
         </is>
       </c>
     </row>
@@ -8703,7 +8703,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18207</t>
+          <t>19616</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>848</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6643</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>949</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18867</t>
+          <t>20155</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>985</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27859</t>
+          <t>28430</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,7 +8846,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>2491</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32181</t>
+          <t>31506</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8222</t>
+          <t>8261</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>100844</t>
+          <t>99894</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11586</t>
+          <t>11966</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24916</t>
+          <t>24599</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16706</t>
+          <t>16283</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>108547</t>
+          <t>108055</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,06%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9683</t>
+          <t>9544</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>112123</t>
+          <t>109494</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24582</t>
+          <t>23698</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41109</t>
+          <t>40379</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22303</t>
+          <t>24156</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>143394</t>
+          <t>146561</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>155475</t>
+          <t>156552</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>372729</t>
+          <t>368440</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49118</t>
+          <t>49967</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>68484</t>
+          <t>67851</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>225455</t>
+          <t>223172</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>466033</t>
+          <t>460480</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>89,76%</t>
         </is>
       </c>
     </row>
@@ -9385,7 +9385,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7738</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>598</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>5136</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1547</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>9825</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12376</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2272</t>
+          <t>2213</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11464</t>
+          <t>12305</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18642</t>
+          <t>19500</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15564</t>
+          <t>16958</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34260</t>
+          <t>34683</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15551</t>
+          <t>14896</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29115</t>
+          <t>29162</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>33556</t>
+          <t>35327</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>58306</t>
+          <t>59408</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,64%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10975</t>
+          <t>11238</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28307</t>
+          <t>29586</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9575</t>
+          <t>9376</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21579</t>
+          <t>20898</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23843</t>
+          <t>23525</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46556</t>
+          <t>44393</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>28,13%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18249</t>
+          <t>16893</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>36202</t>
+          <t>35429</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29365</t>
+          <t>29243</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46070</t>
+          <t>45281</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>51822</t>
+          <t>50792</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>75937</t>
+          <t>75224</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>47,66%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8256</t>
+          <t>8022</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22603</t>
+          <t>21984</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11421</t>
+          <t>11099</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13262</t>
+          <t>13287</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30025</t>
+          <t>30302</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2837</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15920</t>
+          <t>17598</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7359</t>
+          <t>7271</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>5597</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>19638</t>
+          <t>20816</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9184</t>
+          <t>9858</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24040</t>
+          <t>24449</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>7795</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19221</t>
+          <t>19038</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>20138</t>
+          <t>19768</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>39410</t>
+          <t>38866</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,75%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19064</t>
+          <t>19191</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37718</t>
+          <t>38379</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21223</t>
+          <t>20408</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35419</t>
+          <t>35361</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>43578</t>
+          <t>43077</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>67229</t>
+          <t>67068</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,08%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>33045</t>
+          <t>32436</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>53440</t>
+          <t>53646</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>30984</t>
+          <t>31877</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>47750</t>
+          <t>47307</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>69319</t>
+          <t>68248</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>97053</t>
+          <t>95795</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>48,68%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7642</t>
+          <t>7682</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>41337</t>
+          <t>42728</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>9897</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>24352</t>
+          <t>23404</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>16985</t>
+          <t>16349</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>56931</t>
+          <t>56049</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9689</t>
+          <t>10198</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>51538</t>
+          <t>50970</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9747</t>
+          <t>9732</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>22865</t>
+          <t>23600</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>20984</t>
+          <t>17243</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>64789</t>
+          <t>62849</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>28426</t>
+          <t>31733</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>131908</t>
+          <t>136917</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>51313</t>
+          <t>50903</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>74273</t>
+          <t>74222</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>70906</t>
+          <t>68144</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>195876</t>
+          <t>195171</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>40444</t>
+          <t>40575</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>183101</t>
+          <t>184829</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>78386</t>
+          <t>79002</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>107216</t>
+          <t>108230</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>100491</t>
+          <t>84104</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>274830</t>
+          <t>272495</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,58%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>280425</t>
+          <t>277185</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>578083</t>
+          <t>569652</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>153154</t>
+          <t>153925</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>187169</t>
+          <t>186984</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>455202</t>
+          <t>458514</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>804476</t>
+          <t>839473</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>81,89%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6703-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6703-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>988</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9285</t>
+          <t>9808</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10810</t>
+          <t>11822</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2888</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18081</t>
+          <t>16401</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10692</t>
+          <t>10952</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11334</t>
+          <t>11473</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16961</t>
+          <t>18083</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39428</t>
+          <t>38696</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>63573</t>
+          <t>63103</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21000</t>
+          <t>21158</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>41774</t>
+          <t>41281</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>64784</t>
+          <t>65290</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>96559</t>
+          <t>98651</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66621</t>
+          <t>67789</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>99188</t>
+          <t>98342</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38512</t>
+          <t>39002</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62106</t>
+          <t>62559</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>113503</t>
+          <t>112768</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>152548</t>
+          <t>150775</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,05%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>111100</t>
+          <t>111840</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>144753</t>
+          <t>145530</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>59463</t>
+          <t>59619</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>85740</t>
+          <t>85196</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>181254</t>
+          <t>181902</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>221825</t>
+          <t>224726</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>52,24%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>1908</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11414</t>
+          <t>11180</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>2318</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13007</t>
+          <t>13536</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,47 +1464,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>11554</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>5958</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>19816</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>0,87%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>4,79%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>11554</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>6086</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>19938</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>5257</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20081</t>
+          <t>18972</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4490</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17740</t>
+          <t>17601</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12752</t>
+          <t>13117</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32512</t>
+          <t>31035</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56602</t>
+          <t>57089</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>88900</t>
+          <t>88710</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33646</t>
+          <t>33650</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60843</t>
+          <t>59784</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>99748</t>
+          <t>98131</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>139771</t>
+          <t>137582</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>99083</t>
+          <t>98734</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>139032</t>
+          <t>135263</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69500</t>
+          <t>68880</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102065</t>
+          <t>100589</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>176664</t>
+          <t>178056</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>226103</t>
+          <t>226315</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,22%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>184302</t>
+          <t>183435</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>227135</t>
+          <t>227404</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>107762</t>
+          <t>109803</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>141336</t>
+          <t>144060</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>302289</t>
+          <t>305371</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>358092</t>
+          <t>357843</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>52,52%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13332</t>
+          <t>13434</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2359</t>
+          <t>2392</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15645</t>
+          <t>15767</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7248</t>
+          <t>7142</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23550</t>
+          <t>22808</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17103</t>
+          <t>16552</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12979</t>
+          <t>12889</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6214</t>
+          <t>6689</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24182</t>
+          <t>23658</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36694</t>
+          <t>36320</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>64373</t>
+          <t>65032</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19102</t>
+          <t>18475</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>39814</t>
+          <t>39473</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>59646</t>
+          <t>59486</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>94576</t>
+          <t>95913</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74930</t>
+          <t>75572</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>109537</t>
+          <t>108949</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50232</t>
+          <t>49317</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>80016</t>
+          <t>79407</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>135188</t>
+          <t>134789</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>178363</t>
+          <t>178864</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,32%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>148335</t>
+          <t>150232</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>188626</t>
+          <t>188774</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>92555</t>
+          <t>92696</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>122146</t>
+          <t>124535</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>252324</t>
+          <t>251350</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>299504</t>
+          <t>299283</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>55,76%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6982</t>
+          <t>6810</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22979</t>
+          <t>21810</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6768</t>
+          <t>6558</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21134</t>
+          <t>21617</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16614</t>
+          <t>16394</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38037</t>
+          <t>37170</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6830</t>
+          <t>6624</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21062</t>
+          <t>20940</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>20308</t>
+          <t>20403</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>16367</t>
+          <t>16561</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>35809</t>
+          <t>36055</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>81684</t>
+          <t>82141</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>117964</t>
+          <t>117120</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>56371</t>
+          <t>56949</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>85058</t>
+          <t>86619</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>147810</t>
+          <t>146136</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>192868</t>
+          <t>194009</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,86%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>119027</t>
+          <t>118934</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>158555</t>
+          <t>159520</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>65647</t>
+          <t>64496</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>97632</t>
+          <t>95976</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>192055</t>
+          <t>194844</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>245811</t>
+          <t>245019</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,92%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>137516</t>
+          <t>138221</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>177884</t>
+          <t>179770</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>109430</t>
+          <t>108280</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>143604</t>
+          <t>142390</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>256575</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>311842</t>
+          <t>310236</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>42,95%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>18657</t>
+          <t>17753</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>40247</t>
+          <t>38948</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>20062</t>
+          <t>19494</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>43226</t>
+          <t>42850</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>42199</t>
+          <t>43342</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>75410</t>
+          <t>73677</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24167</t>
+          <t>22667</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>49097</t>
+          <t>46822</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>23543</t>
+          <t>23408</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>47785</t>
+          <t>46078</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>52717</t>
+          <t>53103</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>84535</t>
+          <t>87411</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>239966</t>
+          <t>239989</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>299027</t>
+          <t>301776</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>147794</t>
+          <t>150646</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>198636</t>
+          <t>200046</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>406423</t>
+          <t>404977</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>482096</t>
+          <t>484093</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>393242</t>
+          <t>396048</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>467545</t>
+          <t>466308</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>248692</t>
+          <t>251447</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>306944</t>
+          <t>309988</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>664296</t>
+          <t>660794</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>757598</t>
+          <t>755024</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,85%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>617714</t>
+          <t>621850</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>697278</t>
+          <t>699229</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>397847</t>
+          <t>400927</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>466188</t>
+          <t>463240</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1043574</t>
+          <t>1043749</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1144173</t>
+          <t>1142433</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,19%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3387</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16115</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,82 +4389,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>6,94%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>10082</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5453</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>17308</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>6,02%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>10,34%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>18087</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>10549</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>27201</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>6,62%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>10082</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>5290</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>17793</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>10,63%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>18087</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>11585</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>29047</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23154</t>
+          <t>21943</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>6281</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20556</t>
+          <t>19590</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17798</t>
+          <t>18310</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36304</t>
+          <t>37195</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45257</t>
+          <t>47013</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>71795</t>
+          <t>72556</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20423</t>
+          <t>20378</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39704</t>
+          <t>39627</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>71505</t>
+          <t>72331</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>104177</t>
+          <t>105780</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,76%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65002</t>
+          <t>63690</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>94502</t>
+          <t>93171</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33876</t>
+          <t>33788</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54760</t>
+          <t>55646</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>105616</t>
+          <t>102941</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>141274</t>
+          <t>140461</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,2%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>68856</t>
+          <t>70157</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>98700</t>
+          <t>100486</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>59400</t>
+          <t>60610</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>83875</t>
+          <t>85040</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>137666</t>
+          <t>136801</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>175308</t>
+          <t>177290</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>43,17%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6466</t>
+          <t>6474</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22336</t>
+          <t>20923</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>4306</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16717</t>
+          <t>16381</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13888</t>
+          <t>13758</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33121</t>
+          <t>33069</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15122</t>
+          <t>14937</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33943</t>
+          <t>33272</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>8290</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23506</t>
+          <t>23482</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26839</t>
+          <t>26662</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51746</t>
+          <t>50970</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>58167</t>
+          <t>58257</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>90970</t>
+          <t>91528</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>38939</t>
+          <t>37802</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63240</t>
+          <t>62716</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>102534</t>
+          <t>104499</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>145519</t>
+          <t>143924</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>122167</t>
+          <t>122957</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>162068</t>
+          <t>164148</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67695</t>
+          <t>66815</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>96868</t>
+          <t>98981</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>200419</t>
+          <t>197099</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>250129</t>
+          <t>246539</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>35,84%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>142382</t>
+          <t>144124</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>184745</t>
+          <t>183483</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>101978</t>
+          <t>99143</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>134400</t>
+          <t>133518</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>256338</t>
+          <t>256246</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>310189</t>
+          <t>308986</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>44,92%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4257</t>
+          <t>4249</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16896</t>
+          <t>18122</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14053</t>
+          <t>14947</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10408</t>
+          <t>10615</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27046</t>
+          <t>28428</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9528</t>
+          <t>9709</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28396</t>
+          <t>28028</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11156</t>
+          <t>10989</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27929</t>
+          <t>27510</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23803</t>
+          <t>24234</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47762</t>
+          <t>49427</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>61309</t>
+          <t>59121</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>92659</t>
+          <t>92358</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32970</t>
+          <t>33455</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58321</t>
+          <t>59579</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>101001</t>
+          <t>100999</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>141143</t>
+          <t>141773</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,35%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>93909</t>
+          <t>94901</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>130222</t>
+          <t>134060</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55432</t>
+          <t>54646</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>83327</t>
+          <t>82034</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>158505</t>
+          <t>157174</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>205739</t>
+          <t>202764</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>31,96%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>129406</t>
+          <t>130901</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>169285</t>
+          <t>170508</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>115619</t>
+          <t>115628</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>147537</t>
+          <t>148297</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>253578</t>
+          <t>255420</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>306416</t>
+          <t>308258</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,59%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20420</t>
+          <t>20243</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4275</t>
+          <t>4166</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17684</t>
+          <t>16484</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13373</t>
+          <t>13439</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31627</t>
+          <t>31636</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13766</t>
+          <t>13376</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>31178</t>
+          <t>30524</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8731</t>
+          <t>9658</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24249</t>
+          <t>24340</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>25728</t>
+          <t>25928</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>50290</t>
+          <t>49159</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>47575</t>
+          <t>48652</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>77360</t>
+          <t>76450</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>38441</t>
+          <t>38412</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>64846</t>
+          <t>64322</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>93453</t>
+          <t>93173</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>133201</t>
+          <t>135413</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,64%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>116151</t>
+          <t>116944</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>153463</t>
+          <t>154929</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>99262</t>
+          <t>100575</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>134870</t>
+          <t>132937</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>227150</t>
+          <t>227795</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>277842</t>
+          <t>276829</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,1%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>152950</t>
+          <t>153385</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>192490</t>
+          <t>192410</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>115712</t>
+          <t>116202</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>151011</t>
+          <t>152751</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>279855</t>
+          <t>277161</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>333832</t>
+          <t>333557</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>45,9%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29794</t>
+          <t>29198</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>56535</t>
+          <t>54754</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>26687</t>
+          <t>26770</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>51660</t>
+          <t>51009</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>59932</t>
+          <t>61172</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>95916</t>
+          <t>96014</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>58898</t>
+          <t>57991</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>94908</t>
+          <t>92533</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>46071</t>
+          <t>47616</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>76891</t>
+          <t>78155</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>112570</t>
+          <t>114209</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>158886</t>
+          <t>161380</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>241635</t>
+          <t>242647</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>302758</t>
+          <t>303751</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>150133</t>
+          <t>148891</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>198083</t>
+          <t>197227</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>405708</t>
+          <t>405899</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>485182</t>
+          <t>481489</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,58%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>432259</t>
+          <t>428687</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>503993</t>
+          <t>503720</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>282652</t>
+          <t>278017</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>343557</t>
+          <t>336945</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>730550</t>
+          <t>733737</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>823800</t>
+          <t>825318</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,56%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>531787</t>
+          <t>533444</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>607872</t>
+          <t>610094</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>422213</t>
+          <t>425093</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>486106</t>
+          <t>489558</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>978164</t>
+          <t>978782</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1082131</t>
+          <t>1078964</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>43,87%</t>
         </is>
       </c>
     </row>
@@ -8011,7 +8011,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -8021,12 +8021,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>6208</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8046,32 +8046,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4719</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10459</t>
+          <t>12527</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8081,32 +8081,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>6329</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2526</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13362</t>
+          <t>15615</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -8124,32 +8124,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6594</t>
+          <t>6527</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14044</t>
+          <t>13241</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1126</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8194,32 +8194,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>7720</t>
+          <t>7700</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3464</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14192</t>
+          <t>15086</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -8237,32 +8237,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>6740</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12074</t>
+          <t>13575</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8272,32 +8272,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10192</t>
+          <t>10803</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5827</t>
+          <t>6137</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15805</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8307,32 +8307,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>15519</t>
+          <t>17544</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10198</t>
+          <t>11259</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23736</t>
+          <t>25477</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,48%</t>
         </is>
       </c>
     </row>
@@ -8350,32 +8350,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23817</t>
+          <t>24517</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15570</t>
+          <t>14509</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37738</t>
+          <t>36257</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8385,32 +8385,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17978</t>
+          <t>20496</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>13912</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26197</t>
+          <t>29751</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8420,32 +8420,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>41795</t>
+          <t>45013</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29521</t>
+          <t>33297</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56968</t>
+          <t>60036</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>34,12%</t>
         </is>
       </c>
     </row>
@@ -8463,32 +8463,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>51921</t>
+          <t>59144</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38920</t>
+          <t>46704</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>62140</t>
+          <t>71512</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8498,32 +8498,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>34557</t>
+          <t>40218</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27183</t>
+          <t>31371</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41527</t>
+          <t>47754</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8533,32 +8533,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>86479</t>
+          <t>99362</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>71484</t>
+          <t>83636</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>99895</t>
+          <t>113627</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>64,58%</t>
         </is>
       </c>
     </row>
@@ -8576,17 +8576,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88889</t>
+          <t>98165</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88889</t>
+          <t>98165</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88889</t>
+          <t>98165</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8611,17 +8611,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>68573</t>
+          <t>77782</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68573</t>
+          <t>77782</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68573</t>
+          <t>77782</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8646,17 +8646,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>157462</t>
+          <t>175947</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>157462</t>
+          <t>175947</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>157462</t>
+          <t>175947</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8693,32 +8693,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5378</t>
+          <t>7982</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19616</t>
+          <t>17762</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8728,32 +8728,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2497</t>
+          <t>3671</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8763,32 +8763,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>7875</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>6393</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20155</t>
+          <t>22962</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -8806,32 +8806,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8382</t>
+          <t>8757</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>3720</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28430</t>
+          <t>16786</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8841,67 +8841,67 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5752</t>
+          <t>6074</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2804</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10951</t>
+          <t>11165</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>8,71%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>14831</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>8747</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>25461</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t>4,94%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>9,4%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>14134</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>2491</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>31506</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -8919,32 +8919,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34936</t>
+          <t>40366</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8261</t>
+          <t>29308</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>99894</t>
+          <t>54195</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8954,32 +8954,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17545</t>
+          <t>18551</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11966</t>
+          <t>12039</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24599</t>
+          <t>25610</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8989,32 +8989,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>52481</t>
+          <t>58916</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16283</t>
+          <t>44994</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>108055</t>
+          <t>73641</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -9032,32 +9032,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>39256</t>
+          <t>42044</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9544</t>
+          <t>31121</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>109494</t>
+          <t>55091</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9067,32 +9067,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31788</t>
+          <t>36329</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23698</t>
+          <t>28140</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40379</t>
+          <t>45706</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9102,32 +9102,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>71044</t>
+          <t>78373</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24156</t>
+          <t>63084</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>146561</t>
+          <t>97480</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>32,48%</t>
         </is>
       </c>
     </row>
@@ -9145,32 +9145,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>308618</t>
+          <t>72750</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>156552</t>
+          <t>56853</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>368440</t>
+          <t>86176</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9180,32 +9180,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>58874</t>
+          <t>63623</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49967</t>
+          <t>54376</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>67851</t>
+          <t>73711</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9215,32 +9215,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>367492</t>
+          <t>136373</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>223172</t>
+          <t>118342</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>460480</t>
+          <t>154046</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>51,32%</t>
         </is>
       </c>
     </row>
@@ -9258,17 +9258,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>396570</t>
+          <t>171899</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>396570</t>
+          <t>171899</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>396570</t>
+          <t>171899</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9293,17 +9293,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>116456</t>
+          <t>128248</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>116456</t>
+          <t>128248</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>116456</t>
+          <t>128248</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9328,17 +9328,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>513026</t>
+          <t>300147</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>513026</t>
+          <t>300147</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>513026</t>
+          <t>300147</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9375,32 +9375,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2236</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>960</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7616</t>
+          <t>12775</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9410,32 +9410,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>614</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5136</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9445,32 +9445,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>4147</t>
+          <t>6447</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>2225</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9825</t>
+          <t>14517</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -9488,32 +9488,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5734</t>
+          <t>5918</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>2208</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>12976</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9523,32 +9523,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5427</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t>2188</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12305</t>
+          <t>11568</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9558,32 +9558,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>11160</t>
+          <t>11537</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19500</t>
+          <t>19601</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -9601,32 +9601,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>24334</t>
+          <t>28615</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16958</t>
+          <t>18610</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34683</t>
+          <t>40040</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9636,32 +9636,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>21675</t>
+          <t>26185</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14896</t>
+          <t>19377</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29162</t>
+          <t>35187</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9671,32 +9671,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>46009</t>
+          <t>54801</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>35327</t>
+          <t>42409</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>59408</t>
+          <t>69022</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,38%</t>
         </is>
       </c>
     </row>
@@ -9714,32 +9714,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18687</t>
+          <t>21357</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11238</t>
+          <t>12879</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29586</t>
+          <t>32842</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9749,32 +9749,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14563</t>
+          <t>15808</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9376</t>
+          <t>10551</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20898</t>
+          <t>24197</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9784,32 +9784,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>33249</t>
+          <t>37165</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23525</t>
+          <t>26901</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>44393</t>
+          <t>51488</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,88%</t>
         </is>
       </c>
     </row>
@@ -9827,32 +9827,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>26024</t>
+          <t>32791</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16893</t>
+          <t>22968</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35429</t>
+          <t>45116</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9862,32 +9862,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>37248</t>
+          <t>41915</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29243</t>
+          <t>32989</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>45281</t>
+          <t>50396</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9897,32 +9897,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>63272</t>
+          <t>74706</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>50792</t>
+          <t>61416</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>75224</t>
+          <t>91761</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>49,69%</t>
         </is>
       </c>
     </row>
@@ -9940,17 +9940,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>77014</t>
+          <t>93124</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>77014</t>
+          <t>93124</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>77014</t>
+          <t>93124</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9975,17 +9975,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>80824</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>80824</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>80824</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10010,17 +10010,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>157838</t>
+          <t>184655</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>157838</t>
+          <t>184655</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>157838</t>
+          <t>184655</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>14244</t>
+          <t>15086</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>8580</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21984</t>
+          <t>26442</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6255</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3873</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11099</t>
+          <t>13012</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>20499</t>
+          <t>22771</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13287</t>
+          <t>15402</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30302</t>
+          <t>34299</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -10170,32 +10170,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>7580</t>
+          <t>7550</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17598</t>
+          <t>17459</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10205,32 +10205,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3296</t>
+          <t>3996</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>1572</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7271</t>
+          <t>9334</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10240,32 +10240,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>10876</t>
+          <t>11545</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5597</t>
+          <t>5971</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>20816</t>
+          <t>21015</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -10283,32 +10283,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>15772</t>
+          <t>16031</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9858</t>
+          <t>10168</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24449</t>
+          <t>25019</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10318,32 +10318,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>12409</t>
+          <t>14443</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7795</t>
+          <t>9160</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19038</t>
+          <t>21594</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10353,32 +10353,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>28181</t>
+          <t>30474</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>19768</t>
+          <t>21853</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>38866</t>
+          <t>40835</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,02%</t>
         </is>
       </c>
     </row>
@@ -10396,32 +10396,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>27288</t>
+          <t>29920</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19191</t>
+          <t>21352</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38379</t>
+          <t>40652</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10431,32 +10431,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>27487</t>
+          <t>29713</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>20408</t>
+          <t>22017</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35361</t>
+          <t>38175</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10466,32 +10466,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>54775</t>
+          <t>59633</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>43077</t>
+          <t>47307</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>67068</t>
+          <t>72822</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,93%</t>
         </is>
       </c>
     </row>
@@ -10509,32 +10509,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>42766</t>
+          <t>48190</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>32436</t>
+          <t>36533</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>53646</t>
+          <t>59791</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10544,32 +10544,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>39705</t>
+          <t>42029</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>31877</t>
+          <t>33816</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>47307</t>
+          <t>51006</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10579,32 +10579,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>82471</t>
+          <t>90219</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>68248</t>
+          <t>75751</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>95795</t>
+          <t>105518</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>49,16%</t>
         </is>
       </c>
     </row>
@@ -10622,17 +10622,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>107650</t>
+          <t>116777</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>107650</t>
+          <t>116777</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>107650</t>
+          <t>116777</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10657,17 +10657,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>89152</t>
+          <t>97866</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>89152</t>
+          <t>97866</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>89152</t>
+          <t>97866</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10692,17 +10692,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>196802</t>
+          <t>214643</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>196802</t>
+          <t>214643</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>196802</t>
+          <t>214643</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>23087</t>
+          <t>28747</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7682</t>
+          <t>17961</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>42728</t>
+          <t>42734</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>15383</t>
+          <t>18452</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>12253</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>23404</t>
+          <t>27400</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>38470</t>
+          <t>47199</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>16349</t>
+          <t>33770</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>56049</t>
+          <t>65246</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -10852,32 +10852,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>28290</t>
+          <t>28752</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10198</t>
+          <t>19084</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>50970</t>
+          <t>43489</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10887,32 +10887,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>15601</t>
+          <t>16861</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9732</t>
+          <t>10529</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>23600</t>
+          <t>25611</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10922,32 +10922,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>43891</t>
+          <t>45613</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>17243</t>
+          <t>33890</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>62849</t>
+          <t>61477</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -10965,32 +10965,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>80369</t>
+          <t>91752</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>31733</t>
+          <t>73553</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>136917</t>
+          <t>112920</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11000,32 +11000,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>61821</t>
+          <t>69983</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>50903</t>
+          <t>56549</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>74222</t>
+          <t>84122</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11035,32 +11035,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>142191</t>
+          <t>161735</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>68144</t>
+          <t>140107</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>195171</t>
+          <t>183832</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -11078,32 +11078,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>109047</t>
+          <t>117838</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>40575</t>
+          <t>96630</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>184829</t>
+          <t>139186</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11113,32 +11113,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>91815</t>
+          <t>102347</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>79002</t>
+          <t>87638</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>108230</t>
+          <t>119784</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11148,32 +11148,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>200863</t>
+          <t>220185</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>84104</t>
+          <t>193254</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>272495</t>
+          <t>247758</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>28,3%</t>
         </is>
       </c>
     </row>
@@ -11191,32 +11191,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>429329</t>
+          <t>212876</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>277185</t>
+          <t>186323</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>569652</t>
+          <t>239509</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11226,32 +11226,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>170385</t>
+          <t>187785</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>153925</t>
+          <t>170313</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>186984</t>
+          <t>206127</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11261,32 +11261,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>599714</t>
+          <t>400661</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>458514</t>
+          <t>369767</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>839473</t>
+          <t>430117</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>49,13%</t>
         </is>
       </c>
     </row>
@@ -11304,17 +11304,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>670123</t>
+          <t>479964</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>670123</t>
+          <t>479964</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>670123</t>
+          <t>479964</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11339,17 +11339,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>355005</t>
+          <t>395428</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>355005</t>
+          <t>395428</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>355005</t>
+          <t>395428</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11374,17 +11374,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1025129</t>
+          <t>875392</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1025129</t>
+          <t>875392</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1025129</t>
+          <t>875392</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
